--- a/crisscross_kit/crisscross/dna_source_plates/assembly_plates/P3651_MA_H5_handles_S1C.xlsx
+++ b/crisscross_kit/crisscross/dna_source_plates/assembly_plates/P3651_MA_H5_handles_S1C.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10302"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/matt/Documents/Shih_Lab_Postdoc/research_projects/crisscross_code/crisscross_kit/crisscross/dna_source_plates/assembly_plates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BD1EC9C-5DFE-004C-9B37-C197919D8DA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAF85645-2F61-0C46-B23E-0ABEBBC1F570}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25600" yWindow="620" windowWidth="25600" windowHeight="28180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1750" uniqueCount="1197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1751" uniqueCount="1198">
   <si>
     <t>name</t>
   </si>
@@ -3613,6 +3613,9 @@
   </si>
   <si>
     <t>P</t>
+  </si>
+  <si>
+    <t>well</t>
   </si>
 </sst>
 </file>
@@ -4005,8 +4008,8 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="1">
-        <v>200</v>
+      <c r="A1" s="1" t="s">
+        <v>1197</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
